--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,7 +4725,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757637</v>
+        <v>122758257</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -4761,7 +4761,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4770,13 +4770,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585636</v>
+        <v>585735</v>
       </c>
       <c r="R41" t="n">
-        <v>7059970</v>
+        <v>7059987</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,24 +4803,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,19 +4825,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757680</v>
+        <v>122757367</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4892,13 +4882,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585688</v>
+        <v>585662</v>
       </c>
       <c r="R42" t="n">
-        <v>7059983</v>
+        <v>7059890</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4925,14 +4915,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4947,22 +4947,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4975,42 +4975,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R43" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5037,14 +5032,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5059,19 +5059,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122756445</v>
+        <v>122757680</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5116,13 +5116,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585841</v>
+        <v>585688</v>
       </c>
       <c r="R44" t="n">
-        <v>7059850</v>
+        <v>7059983</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5149,24 +5149,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5181,22 +5171,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757549</v>
+        <v>122756445</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5209,37 +5199,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585660</v>
+        <v>585841</v>
       </c>
       <c r="R45" t="n">
-        <v>7059938</v>
+        <v>7059850</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5266,9 +5261,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5283,19 +5293,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757492</v>
+        <v>122757637</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5340,10 +5350,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585665</v>
+        <v>585636</v>
       </c>
       <c r="R46" t="n">
-        <v>7059914</v>
+        <v>7059970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5375,7 +5385,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5385,7 +5395,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5539,10 +5549,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757908</v>
+        <v>122757549</v>
       </c>
       <c r="B48" t="n">
-        <v>82549</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5555,21 +5565,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5579,13 +5589,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585747</v>
+        <v>585660</v>
       </c>
       <c r="R48" t="n">
-        <v>7059980</v>
+        <v>7059938</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5612,19 +5622,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,19 +5639,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122757367</v>
+        <v>122757492</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585662</v>
+        <v>585665</v>
       </c>
       <c r="R49" t="n">
-        <v>7059890</v>
+        <v>7059914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,42 +4741,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R41" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,14 +4798,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4825,19 +4825,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757367</v>
+        <v>122756445</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585662</v>
+        <v>585841</v>
       </c>
       <c r="R42" t="n">
-        <v>7059890</v>
+        <v>7059850</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -4959,10 +4959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757908</v>
+        <v>122757492</v>
       </c>
       <c r="B43" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4975,34 +4975,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585747</v>
+        <v>585665</v>
       </c>
       <c r="R43" t="n">
-        <v>7059980</v>
+        <v>7059914</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5044,7 +5049,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5071,7 +5081,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757680</v>
+        <v>122757637</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5116,13 +5126,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585688</v>
+        <v>585636</v>
       </c>
       <c r="R44" t="n">
-        <v>7059983</v>
+        <v>7059970</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5149,14 +5159,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,19 +5191,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122756445</v>
+        <v>122758257</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5219,7 +5239,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5228,13 +5248,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585841</v>
+        <v>585735</v>
       </c>
       <c r="R45" t="n">
-        <v>7059850</v>
+        <v>7059987</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5261,24 +5281,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,19 +5303,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757637</v>
+        <v>122757367</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5350,10 +5360,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585636</v>
+        <v>585662</v>
       </c>
       <c r="R46" t="n">
-        <v>7059970</v>
+        <v>7059890</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5385,7 +5395,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5395,7 +5405,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5427,7 +5437,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122758139</v>
+        <v>122757680</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5472,13 +5482,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585743</v>
+        <v>585688</v>
       </c>
       <c r="R47" t="n">
-        <v>7059982</v>
+        <v>7059983</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5505,24 +5515,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,12 +5537,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122757492</v>
+        <v>122758139</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585665</v>
+        <v>585743</v>
       </c>
       <c r="R49" t="n">
-        <v>7059914</v>
+        <v>7059982</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B41" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,37 +4741,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R41" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4798,19 +4803,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4825,22 +4825,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122756445</v>
+        <v>122757908</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4853,39 +4853,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585841</v>
+        <v>585747</v>
       </c>
       <c r="R42" t="n">
-        <v>7059850</v>
+        <v>7059980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4917,7 +4912,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4927,12 +4922,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4959,7 +4949,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757492</v>
+        <v>122757637</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5004,10 +4994,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585665</v>
+        <v>585636</v>
       </c>
       <c r="R43" t="n">
-        <v>7059914</v>
+        <v>7059970</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5039,7 +5029,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5049,7 +5039,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5081,10 +5071,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757637</v>
+        <v>122757549</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5097,42 +5087,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585636</v>
+        <v>585660</v>
       </c>
       <c r="R44" t="n">
-        <v>7059970</v>
+        <v>7059938</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5159,24 +5144,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5191,19 +5161,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122758257</v>
+        <v>122757492</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5239,7 +5209,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5248,13 +5218,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585735</v>
+        <v>585665</v>
       </c>
       <c r="R45" t="n">
-        <v>7059987</v>
+        <v>7059914</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5281,14 +5251,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5303,19 +5283,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757367</v>
+        <v>122756445</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5360,10 +5340,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585662</v>
+        <v>585841</v>
       </c>
       <c r="R46" t="n">
-        <v>7059890</v>
+        <v>7059850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,7 +5375,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5405,7 +5385,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5549,10 +5529,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757549</v>
+        <v>122758139</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,37 +5545,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585660</v>
+        <v>585743</v>
       </c>
       <c r="R48" t="n">
-        <v>7059938</v>
+        <v>7059982</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5622,9 +5607,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,19 +5639,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122758139</v>
+        <v>122757367</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585743</v>
+        <v>585662</v>
       </c>
       <c r="R49" t="n">
-        <v>7059982</v>
+        <v>7059890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122758257</v>
+        <v>122757549</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,39 +4741,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585735</v>
+        <v>585660</v>
       </c>
       <c r="R41" t="n">
-        <v>7059987</v>
+        <v>7059938</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4806,11 +4801,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4949,7 +4939,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757637</v>
+        <v>122756445</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -4994,10 +4984,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585636</v>
+        <v>585841</v>
       </c>
       <c r="R43" t="n">
-        <v>7059970</v>
+        <v>7059850</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5029,7 +5019,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5039,7 +5029,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5071,10 +5061,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757549</v>
+        <v>122758257</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5087,34 +5077,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585660</v>
+        <v>585735</v>
       </c>
       <c r="R44" t="n">
-        <v>7059938</v>
+        <v>7059987</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5147,6 +5142,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5173,7 +5173,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757492</v>
+        <v>122757680</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585665</v>
+        <v>585688</v>
       </c>
       <c r="R45" t="n">
-        <v>7059914</v>
+        <v>7059983</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5251,24 +5251,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5283,19 +5273,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122756445</v>
+        <v>122758139</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5340,10 +5330,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585841</v>
+        <v>585743</v>
       </c>
       <c r="R46" t="n">
-        <v>7059850</v>
+        <v>7059982</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5375,7 +5365,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5385,7 +5375,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5417,7 +5407,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757680</v>
+        <v>122757367</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5462,13 +5452,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585688</v>
+        <v>585662</v>
       </c>
       <c r="R47" t="n">
-        <v>7059983</v>
+        <v>7059890</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5495,14 +5485,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5517,19 +5517,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122758139</v>
+        <v>122757637</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585743</v>
+        <v>585636</v>
       </c>
       <c r="R48" t="n">
-        <v>7059982</v>
+        <v>7059970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122757367</v>
+        <v>122757492</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585662</v>
+        <v>585665</v>
       </c>
       <c r="R49" t="n">
-        <v>7059890</v>
+        <v>7059914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757549</v>
+        <v>122757367</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,37 +4741,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585660</v>
+        <v>585662</v>
       </c>
       <c r="R41" t="n">
-        <v>7059938</v>
+        <v>7059890</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4798,9 +4803,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,22 +4835,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757908</v>
+        <v>122757637</v>
       </c>
       <c r="B42" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4843,34 +4863,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585747</v>
+        <v>585636</v>
       </c>
       <c r="R42" t="n">
-        <v>7059980</v>
+        <v>7059970</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,7 +4927,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4912,7 +4937,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4939,7 +4969,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122756445</v>
+        <v>122758139</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -4984,10 +5014,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585841</v>
+        <v>585743</v>
       </c>
       <c r="R43" t="n">
-        <v>7059850</v>
+        <v>7059982</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5019,7 +5049,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5029,7 +5059,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5061,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122758257</v>
+        <v>122757549</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5077,39 +5107,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585735</v>
+        <v>585660</v>
       </c>
       <c r="R44" t="n">
-        <v>7059987</v>
+        <v>7059938</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5142,11 +5167,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5173,10 +5193,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757680</v>
+        <v>122757908</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5189,42 +5209,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585688</v>
+        <v>585747</v>
       </c>
       <c r="R45" t="n">
-        <v>7059983</v>
+        <v>7059980</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5251,14 +5266,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5273,19 +5293,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122758139</v>
+        <v>122756445</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5330,10 +5350,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585743</v>
+        <v>585841</v>
       </c>
       <c r="R46" t="n">
-        <v>7059982</v>
+        <v>7059850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5365,7 +5385,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5375,7 +5395,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5407,7 +5427,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757367</v>
+        <v>122758257</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5443,7 +5463,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5452,13 +5472,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585662</v>
+        <v>585735</v>
       </c>
       <c r="R47" t="n">
-        <v>7059890</v>
+        <v>7059987</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5485,24 +5505,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5517,19 +5527,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757637</v>
+        <v>122757680</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5574,13 +5584,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585636</v>
+        <v>585688</v>
       </c>
       <c r="R48" t="n">
-        <v>7059970</v>
+        <v>7059983</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5607,24 +5617,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,12 +5639,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757367</v>
+        <v>122757549</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,42 +4741,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585662</v>
+        <v>585660</v>
       </c>
       <c r="R41" t="n">
-        <v>7059890</v>
+        <v>7059938</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,24 +4798,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,12 +4815,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4969,7 +4949,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122758139</v>
+        <v>122756445</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5014,10 +4994,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585743</v>
+        <v>585841</v>
       </c>
       <c r="R43" t="n">
-        <v>7059982</v>
+        <v>7059850</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5049,7 +5029,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5059,7 +5039,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5091,10 +5071,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757549</v>
+        <v>122757680</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5107,34 +5087,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585660</v>
+        <v>585688</v>
       </c>
       <c r="R44" t="n">
-        <v>7059938</v>
+        <v>7059983</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5167,6 +5152,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5193,10 +5183,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757908</v>
+        <v>122757492</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5209,34 +5199,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585747</v>
+        <v>585665</v>
       </c>
       <c r="R45" t="n">
-        <v>7059980</v>
+        <v>7059914</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5268,7 +5263,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5278,7 +5273,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5305,7 +5305,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122756445</v>
+        <v>122758257</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5341,7 +5341,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5350,13 +5350,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585841</v>
+        <v>585735</v>
       </c>
       <c r="R46" t="n">
-        <v>7059850</v>
+        <v>7059987</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5383,24 +5383,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5415,22 +5405,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5443,42 +5433,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R47" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5505,14 +5490,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5527,19 +5517,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757680</v>
+        <v>122757367</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5584,13 +5574,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585688</v>
+        <v>585662</v>
       </c>
       <c r="R48" t="n">
-        <v>7059983</v>
+        <v>7059890</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5617,14 +5607,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5639,19 +5639,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122757492</v>
+        <v>122758139</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585665</v>
+        <v>585743</v>
       </c>
       <c r="R49" t="n">
-        <v>7059914</v>
+        <v>7059982</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757549</v>
+        <v>122757492</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,37 +4741,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585660</v>
+        <v>585665</v>
       </c>
       <c r="R41" t="n">
-        <v>7059938</v>
+        <v>7059914</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4798,9 +4803,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,12 +4835,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4949,7 +4969,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122756445</v>
+        <v>122757367</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -4994,10 +5014,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585841</v>
+        <v>585662</v>
       </c>
       <c r="R43" t="n">
-        <v>7059850</v>
+        <v>7059890</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5029,7 +5049,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5039,7 +5059,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5071,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757680</v>
+        <v>122757549</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5087,39 +5107,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585688</v>
+        <v>585660</v>
       </c>
       <c r="R44" t="n">
-        <v>7059983</v>
+        <v>7059938</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5152,11 +5167,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5183,10 +5193,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757492</v>
+        <v>122757908</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5199,39 +5209,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585665</v>
+        <v>585747</v>
       </c>
       <c r="R45" t="n">
-        <v>7059914</v>
+        <v>7059980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,7 +5268,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5273,12 +5278,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5305,7 +5305,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122758257</v>
+        <v>122756445</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5341,7 +5341,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5350,13 +5350,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585735</v>
+        <v>585841</v>
       </c>
       <c r="R46" t="n">
-        <v>7059987</v>
+        <v>7059850</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5383,14 +5383,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5405,22 +5415,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B47" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5433,37 +5443,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R47" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5490,19 +5505,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5517,19 +5527,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757367</v>
+        <v>122758139</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5574,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585662</v>
+        <v>585743</v>
       </c>
       <c r="R48" t="n">
-        <v>7059890</v>
+        <v>7059982</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5609,7 +5619,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5619,7 +5629,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5651,7 +5661,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122758139</v>
+        <v>122757680</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -5696,13 +5706,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585743</v>
+        <v>585688</v>
       </c>
       <c r="R49" t="n">
-        <v>7059982</v>
+        <v>7059983</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5729,24 +5739,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,12 +5761,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4847,7 +4847,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757637</v>
+        <v>122756445</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585636</v>
+        <v>585841</v>
       </c>
       <c r="R42" t="n">
-        <v>7059970</v>
+        <v>7059850</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -4969,7 +4969,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757367</v>
+        <v>122757680</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5014,13 +5014,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585662</v>
+        <v>585688</v>
       </c>
       <c r="R43" t="n">
-        <v>7059890</v>
+        <v>7059983</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5047,24 +5047,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5079,12 +5069,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5193,10 +5183,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757908</v>
+        <v>122758139</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5209,34 +5199,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585747</v>
+        <v>585743</v>
       </c>
       <c r="R45" t="n">
-        <v>7059980</v>
+        <v>7059982</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5268,7 +5263,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5278,7 +5273,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5305,7 +5305,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122756445</v>
+        <v>122757637</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585841</v>
+        <v>585636</v>
       </c>
       <c r="R46" t="n">
-        <v>7059850</v>
+        <v>7059970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5539,7 +5539,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122758139</v>
+        <v>122757367</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585743</v>
+        <v>585662</v>
       </c>
       <c r="R48" t="n">
-        <v>7059982</v>
+        <v>7059890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5661,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122757680</v>
+        <v>122757908</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5677,42 +5677,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585688</v>
+        <v>585747</v>
       </c>
       <c r="R49" t="n">
-        <v>7059983</v>
+        <v>7059980</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5739,14 +5734,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,12 +5761,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4969,10 +4969,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757680</v>
+        <v>122757549</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4985,39 +4985,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585688</v>
+        <v>585660</v>
       </c>
       <c r="R43" t="n">
-        <v>7059983</v>
+        <v>7059938</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5050,11 +5045,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5081,10 +5071,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757549</v>
+        <v>122757680</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5097,34 +5087,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585660</v>
+        <v>585688</v>
       </c>
       <c r="R44" t="n">
-        <v>7059938</v>
+        <v>7059983</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5157,6 +5152,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757492</v>
+        <v>122757549</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,42 +4741,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585665</v>
+        <v>585660</v>
       </c>
       <c r="R41" t="n">
-        <v>7059914</v>
+        <v>7059938</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,24 +4798,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,22 +4815,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122756445</v>
+        <v>122758139</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4892,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585841</v>
+        <v>585743</v>
       </c>
       <c r="R42" t="n">
-        <v>7059850</v>
+        <v>7059982</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4927,7 +4907,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4937,7 +4917,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -4969,10 +4949,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757549</v>
+        <v>122756445</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4985,37 +4965,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585660</v>
+        <v>585841</v>
       </c>
       <c r="R43" t="n">
-        <v>7059938</v>
+        <v>7059850</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5042,9 +5027,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5059,12 +5059,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5074,7 +5074,7 @@
         <v>122757680</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122758139</v>
+        <v>122757637</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585743</v>
+        <v>585636</v>
       </c>
       <c r="R45" t="n">
-        <v>7059982</v>
+        <v>7059970</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757637</v>
+        <v>122757492</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585636</v>
+        <v>585665</v>
       </c>
       <c r="R46" t="n">
-        <v>7059970</v>
+        <v>7059914</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122758257</v>
+        <v>122757367</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5472,13 +5472,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585735</v>
+        <v>585662</v>
       </c>
       <c r="R47" t="n">
-        <v>7059987</v>
+        <v>7059890</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5505,14 +5505,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5527,22 +5537,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757367</v>
+        <v>122757908</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>82556</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5555,39 +5565,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585662</v>
+        <v>585747</v>
       </c>
       <c r="R48" t="n">
-        <v>7059890</v>
+        <v>7059980</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5619,7 +5624,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5629,12 +5634,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5661,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B49" t="n">
-        <v>82553</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5677,37 +5677,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R49" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5734,19 +5739,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,12 +5761,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757549</v>
+        <v>122758139</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,37 +4741,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585660</v>
+        <v>585743</v>
       </c>
       <c r="R41" t="n">
-        <v>7059938</v>
+        <v>7059982</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4798,9 +4803,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4815,19 +4835,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122758139</v>
+        <v>122757492</v>
       </c>
       <c r="B42" t="n">
         <v>57481</v>
@@ -4872,10 +4892,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585743</v>
+        <v>585665</v>
       </c>
       <c r="R42" t="n">
-        <v>7059982</v>
+        <v>7059914</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4907,7 +4927,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4917,7 +4937,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5071,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757680</v>
+        <v>122757908</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>82558</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5087,42 +5107,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585688</v>
+        <v>585747</v>
       </c>
       <c r="R44" t="n">
-        <v>7059983</v>
+        <v>7059980</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5149,14 +5164,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,19 +5191,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757637</v>
+        <v>122757680</v>
       </c>
       <c r="B45" t="n">
         <v>57481</v>
@@ -5228,13 +5248,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585636</v>
+        <v>585688</v>
       </c>
       <c r="R45" t="n">
-        <v>7059970</v>
+        <v>7059983</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5261,24 +5281,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,22 +5303,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757492</v>
+        <v>122757549</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5321,42 +5331,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585665</v>
+        <v>585660</v>
       </c>
       <c r="R46" t="n">
-        <v>7059914</v>
+        <v>7059938</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5383,24 +5388,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5415,19 +5405,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757367</v>
+        <v>122757637</v>
       </c>
       <c r="B47" t="n">
         <v>57481</v>
@@ -5472,10 +5462,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585662</v>
+        <v>585636</v>
       </c>
       <c r="R47" t="n">
-        <v>7059890</v>
+        <v>7059970</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5507,7 +5497,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5517,7 +5507,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5549,10 +5539,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122757908</v>
+        <v>122757367</v>
       </c>
       <c r="B48" t="n">
-        <v>82556</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,34 +5555,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585747</v>
+        <v>585662</v>
       </c>
       <c r="R48" t="n">
-        <v>7059980</v>
+        <v>7059890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5624,7 +5619,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5634,7 +5629,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5771,6 +5771,842 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125265495</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>585672</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7059874</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125265038</v>
+      </c>
+      <c r="B51" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>585638</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7059956</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125265762</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>585766</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7059797</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125265649</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>585700</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7059842</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125265666</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>585701</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7059838</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125265105</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>585633</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7059942</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125265916</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56112</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>585837</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7059893</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125265542</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>585673</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7059863</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265495</v>
+        <v>125265542</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,25 +5785,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5813,10 +5813,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585672</v>
+        <v>585673</v>
       </c>
       <c r="R50" t="n">
-        <v>7059874</v>
+        <v>7059863</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5875,10 +5875,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265038</v>
+        <v>125265495</v>
       </c>
       <c r="B51" t="n">
-        <v>96227</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5887,25 +5887,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585638</v>
+        <v>585672</v>
       </c>
       <c r="R51" t="n">
-        <v>7059956</v>
+        <v>7059874</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5977,10 +5977,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265762</v>
+        <v>125265666</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5989,43 +5989,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585766</v>
+        <v>585701</v>
       </c>
       <c r="R52" t="n">
-        <v>7059797</v>
+        <v>7059838</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6084,10 +6079,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265649</v>
+        <v>125265038</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6096,25 +6091,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6124,10 +6119,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585700</v>
+        <v>585638</v>
       </c>
       <c r="R53" t="n">
-        <v>7059842</v>
+        <v>7059956</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6186,10 +6181,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265666</v>
+        <v>125265762</v>
       </c>
       <c r="B54" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6198,38 +6193,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585701</v>
+        <v>585766</v>
       </c>
       <c r="R54" t="n">
-        <v>7059838</v>
+        <v>7059797</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265542</v>
+        <v>125265649</v>
       </c>
       <c r="B57" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6519,25 +6519,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585673</v>
+        <v>585700</v>
       </c>
       <c r="R57" t="n">
-        <v>7059863</v>
+        <v>7059842</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265542</v>
+        <v>125265495</v>
       </c>
       <c r="B50" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,25 +5785,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5813,10 +5813,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585673</v>
+        <v>585672</v>
       </c>
       <c r="R50" t="n">
-        <v>7059863</v>
+        <v>7059874</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5875,7 +5875,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265495</v>
+        <v>125265649</v>
       </c>
       <c r="B51" t="n">
         <v>91012</v>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585672</v>
+        <v>585700</v>
       </c>
       <c r="R51" t="n">
-        <v>7059874</v>
+        <v>7059842</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5977,10 +5977,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265666</v>
+        <v>125265762</v>
       </c>
       <c r="B52" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5989,38 +5989,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585701</v>
+        <v>585766</v>
       </c>
       <c r="R52" t="n">
-        <v>7059838</v>
+        <v>7059797</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6079,10 +6084,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265038</v>
+        <v>125265916</v>
       </c>
       <c r="B53" t="n">
-        <v>96227</v>
+        <v>56112</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6091,38 +6096,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>206004</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585638</v>
+        <v>585837</v>
       </c>
       <c r="R53" t="n">
-        <v>7059956</v>
+        <v>7059893</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6181,10 +6191,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265762</v>
+        <v>125265038</v>
       </c>
       <c r="B54" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6193,43 +6203,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585766</v>
+        <v>585638</v>
       </c>
       <c r="R54" t="n">
-        <v>7059797</v>
+        <v>7059956</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6288,10 +6293,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265105</v>
+        <v>125265666</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,43 +6305,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585633</v>
+        <v>585701</v>
       </c>
       <c r="R55" t="n">
-        <v>7059942</v>
+        <v>7059838</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6369,11 +6369,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6400,10 +6395,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265916</v>
+        <v>125265105</v>
       </c>
       <c r="B56" t="n">
-        <v>56112</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6416,27 +6411,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6445,10 +6440,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585837</v>
+        <v>585633</v>
       </c>
       <c r="R56" t="n">
-        <v>7059893</v>
+        <v>7059942</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6481,6 +6476,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265649</v>
+        <v>125265542</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6519,25 +6519,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585700</v>
+        <v>585673</v>
       </c>
       <c r="R57" t="n">
-        <v>7059842</v>
+        <v>7059863</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265495</v>
+        <v>125265762</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5789,34 +5789,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585672</v>
+        <v>585766</v>
       </c>
       <c r="R50" t="n">
-        <v>7059874</v>
+        <v>7059797</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5875,7 +5880,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265649</v>
+        <v>125265495</v>
       </c>
       <c r="B51" t="n">
         <v>91012</v>
@@ -5915,10 +5920,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585700</v>
+        <v>585672</v>
       </c>
       <c r="R51" t="n">
-        <v>7059842</v>
+        <v>7059874</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5977,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265762</v>
+        <v>125265916</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>56112</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5993,27 +5998,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6022,10 +6027,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585766</v>
+        <v>585837</v>
       </c>
       <c r="R52" t="n">
-        <v>7059797</v>
+        <v>7059893</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6084,10 +6089,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265916</v>
+        <v>125265666</v>
       </c>
       <c r="B53" t="n">
-        <v>56112</v>
+        <v>90977</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6096,43 +6101,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585837</v>
+        <v>585701</v>
       </c>
       <c r="R53" t="n">
-        <v>7059893</v>
+        <v>7059838</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,10 +6191,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265038</v>
+        <v>125265105</v>
       </c>
       <c r="B54" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6203,38 +6203,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585638</v>
+        <v>585633</v>
       </c>
       <c r="R54" t="n">
-        <v>7059956</v>
+        <v>7059942</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6267,6 +6272,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6293,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265666</v>
+        <v>125265038</v>
       </c>
       <c r="B55" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6309,21 +6319,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6333,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585701</v>
+        <v>585638</v>
       </c>
       <c r="R55" t="n">
-        <v>7059838</v>
+        <v>7059956</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6395,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265105</v>
+        <v>125265542</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>91361</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6407,43 +6417,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585633</v>
+        <v>585673</v>
       </c>
       <c r="R56" t="n">
-        <v>7059942</v>
+        <v>7059863</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6476,11 +6481,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265542</v>
+        <v>125265649</v>
       </c>
       <c r="B57" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6519,25 +6519,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585673</v>
+        <v>585700</v>
       </c>
       <c r="R57" t="n">
-        <v>7059863</v>
+        <v>7059842</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265762</v>
+        <v>125265542</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>91361</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,43 +5785,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585766</v>
+        <v>585673</v>
       </c>
       <c r="R50" t="n">
-        <v>7059797</v>
+        <v>7059863</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5880,10 +5875,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265495</v>
+        <v>125265666</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5892,25 +5887,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5920,10 +5915,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585672</v>
+        <v>585701</v>
       </c>
       <c r="R51" t="n">
-        <v>7059874</v>
+        <v>7059838</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6089,10 +6084,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265666</v>
+        <v>125265495</v>
       </c>
       <c r="B53" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6101,25 +6096,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6129,10 +6124,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585701</v>
+        <v>585672</v>
       </c>
       <c r="R53" t="n">
-        <v>7059838</v>
+        <v>7059874</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6191,10 +6186,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265105</v>
+        <v>125265649</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6207,39 +6202,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585633</v>
+        <v>585700</v>
       </c>
       <c r="R54" t="n">
-        <v>7059942</v>
+        <v>7059842</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6272,11 +6262,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6303,10 +6288,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265038</v>
+        <v>125265105</v>
       </c>
       <c r="B55" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6315,38 +6300,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585638</v>
+        <v>585633</v>
       </c>
       <c r="R55" t="n">
-        <v>7059956</v>
+        <v>7059942</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6379,6 +6369,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6405,10 +6400,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265542</v>
+        <v>125265038</v>
       </c>
       <c r="B56" t="n">
-        <v>91361</v>
+        <v>96227</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6417,25 +6412,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6440,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585673</v>
+        <v>585638</v>
       </c>
       <c r="R56" t="n">
-        <v>7059863</v>
+        <v>7059956</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6507,10 +6502,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265649</v>
+        <v>125265762</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6523,34 +6518,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585700</v>
+        <v>585766</v>
       </c>
       <c r="R57" t="n">
-        <v>7059842</v>
+        <v>7059797</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6288,10 +6288,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265105</v>
+        <v>125265038</v>
       </c>
       <c r="B55" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,43 +6300,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585633</v>
+        <v>585638</v>
       </c>
       <c r="R55" t="n">
-        <v>7059942</v>
+        <v>7059956</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6369,11 +6364,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6400,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265038</v>
+        <v>125265105</v>
       </c>
       <c r="B56" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6412,38 +6402,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585638</v>
+        <v>585633</v>
       </c>
       <c r="R56" t="n">
-        <v>7059956</v>
+        <v>7059942</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6476,6 +6471,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265542</v>
+        <v>125265105</v>
       </c>
       <c r="B50" t="n">
-        <v>91361</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,38 +5785,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585673</v>
+        <v>585633</v>
       </c>
       <c r="R50" t="n">
-        <v>7059863</v>
+        <v>7059942</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5849,6 +5854,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5875,10 +5885,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265666</v>
+        <v>125265762</v>
       </c>
       <c r="B51" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5887,38 +5897,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585701</v>
+        <v>585766</v>
       </c>
       <c r="R51" t="n">
-        <v>7059838</v>
+        <v>7059797</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5977,10 +5992,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265916</v>
+        <v>125265038</v>
       </c>
       <c r="B52" t="n">
-        <v>56112</v>
+        <v>96227</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5989,43 +6004,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585837</v>
+        <v>585638</v>
       </c>
       <c r="R52" t="n">
-        <v>7059893</v>
+        <v>7059956</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6084,10 +6094,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265495</v>
+        <v>125265916</v>
       </c>
       <c r="B53" t="n">
-        <v>91012</v>
+        <v>56112</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6100,34 +6110,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585672</v>
+        <v>585837</v>
       </c>
       <c r="R53" t="n">
-        <v>7059874</v>
+        <v>7059893</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6288,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265038</v>
+        <v>125265542</v>
       </c>
       <c r="B55" t="n">
-        <v>96227</v>
+        <v>91361</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6328,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585638</v>
+        <v>585673</v>
       </c>
       <c r="R55" t="n">
-        <v>7059956</v>
+        <v>7059863</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6390,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265105</v>
+        <v>125265666</v>
       </c>
       <c r="B56" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,43 +6417,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585633</v>
+        <v>585701</v>
       </c>
       <c r="R56" t="n">
-        <v>7059942</v>
+        <v>7059838</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6471,11 +6481,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6502,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265762</v>
+        <v>125265495</v>
       </c>
       <c r="B57" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6518,39 +6523,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585766</v>
+        <v>585672</v>
       </c>
       <c r="R57" t="n">
-        <v>7059797</v>
+        <v>7059874</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265105</v>
+        <v>125265666</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,43 +5785,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585633</v>
+        <v>585701</v>
       </c>
       <c r="R50" t="n">
-        <v>7059942</v>
+        <v>7059838</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5854,11 +5849,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5885,10 +5875,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265762</v>
+        <v>125265105</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5901,16 +5891,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5921,7 +5911,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5930,10 +5920,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585766</v>
+        <v>585633</v>
       </c>
       <c r="R51" t="n">
-        <v>7059797</v>
+        <v>7059942</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5966,6 +5956,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5992,10 +5987,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265038</v>
+        <v>125265762</v>
       </c>
       <c r="B52" t="n">
-        <v>96227</v>
+        <v>57632</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6004,38 +5999,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585638</v>
+        <v>585766</v>
       </c>
       <c r="R52" t="n">
-        <v>7059956</v>
+        <v>7059797</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6097,7 +6097,7 @@
         <v>125265916</v>
       </c>
       <c r="B53" t="n">
-        <v>56112</v>
+        <v>56226</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265649</v>
+        <v>125265542</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>91521</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,25 +6213,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585700</v>
+        <v>585673</v>
       </c>
       <c r="R54" t="n">
-        <v>7059842</v>
+        <v>7059863</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265542</v>
+        <v>125265038</v>
       </c>
       <c r="B55" t="n">
-        <v>91361</v>
+        <v>96395</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6315,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585673</v>
+        <v>585638</v>
       </c>
       <c r="R55" t="n">
-        <v>7059863</v>
+        <v>7059956</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265666</v>
+        <v>125265495</v>
       </c>
       <c r="B56" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6417,25 +6417,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585701</v>
+        <v>585672</v>
       </c>
       <c r="R56" t="n">
-        <v>7059838</v>
+        <v>7059874</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265495</v>
+        <v>125265649</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585672</v>
+        <v>585700</v>
       </c>
       <c r="R57" t="n">
-        <v>7059874</v>
+        <v>7059842</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265666</v>
+        <v>125265105</v>
       </c>
       <c r="B50" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,38 +5785,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585701</v>
+        <v>585633</v>
       </c>
       <c r="R50" t="n">
-        <v>7059838</v>
+        <v>7059942</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5849,6 +5854,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5875,10 +5885,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265105</v>
+        <v>125265762</v>
       </c>
       <c r="B51" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5891,16 +5901,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5911,7 +5921,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5920,10 +5930,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585633</v>
+        <v>585766</v>
       </c>
       <c r="R51" t="n">
-        <v>7059942</v>
+        <v>7059797</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5956,11 +5966,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5987,10 +5992,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265762</v>
+        <v>125265666</v>
       </c>
       <c r="B52" t="n">
-        <v>57632</v>
+        <v>91131</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5999,43 +6004,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585766</v>
+        <v>585701</v>
       </c>
       <c r="R52" t="n">
-        <v>7059797</v>
+        <v>7059838</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265542</v>
+        <v>125265495</v>
       </c>
       <c r="B54" t="n">
-        <v>91521</v>
+        <v>91166</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,25 +6213,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585673</v>
+        <v>585672</v>
       </c>
       <c r="R54" t="n">
-        <v>7059863</v>
+        <v>7059874</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265038</v>
+        <v>125265542</v>
       </c>
       <c r="B55" t="n">
-        <v>96395</v>
+        <v>91521</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6315,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585638</v>
+        <v>585673</v>
       </c>
       <c r="R55" t="n">
-        <v>7059956</v>
+        <v>7059863</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265495</v>
+        <v>125265038</v>
       </c>
       <c r="B56" t="n">
-        <v>91166</v>
+        <v>96395</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6417,25 +6417,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585672</v>
+        <v>585638</v>
       </c>
       <c r="R56" t="n">
-        <v>7059874</v>
+        <v>7059956</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6405,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265038</v>
+        <v>125265649</v>
       </c>
       <c r="B56" t="n">
-        <v>96395</v>
+        <v>91166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6417,25 +6417,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585638</v>
+        <v>585700</v>
       </c>
       <c r="R56" t="n">
-        <v>7059956</v>
+        <v>7059842</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265649</v>
+        <v>125265038</v>
       </c>
       <c r="B57" t="n">
-        <v>91166</v>
+        <v>96395</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6519,25 +6519,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585700</v>
+        <v>585638</v>
       </c>
       <c r="R57" t="n">
-        <v>7059842</v>
+        <v>7059956</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5773,15 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265105</v>
+        <v>125265495</v>
       </c>
       <c r="B50" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,39 +5784,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585633</v>
+        <v>585672</v>
       </c>
       <c r="R50" t="n">
-        <v>7059942</v>
+        <v>7059874</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5854,11 +5844,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5885,15 +5870,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265762</v>
+        <v>125265649</v>
       </c>
       <c r="B51" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5901,39 +5881,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585766</v>
+        <v>585700</v>
       </c>
       <c r="R51" t="n">
-        <v>7059797</v>
+        <v>7059842</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5992,15 +5967,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265666</v>
+        <v>125265038</v>
       </c>
       <c r="B52" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6008,21 +5978,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6032,10 +6002,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585701</v>
+        <v>585638</v>
       </c>
       <c r="R52" t="n">
-        <v>7059838</v>
+        <v>7059956</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6094,15 +6064,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265916</v>
+        <v>125265105</v>
       </c>
       <c r="B53" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6110,27 +6075,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6139,10 +6104,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585837</v>
+        <v>585633</v>
       </c>
       <c r="R53" t="n">
-        <v>7059893</v>
+        <v>7059942</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6175,6 +6140,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6201,37 +6171,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265495</v>
+        <v>125265542</v>
       </c>
       <c r="B54" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91575</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6241,10 +6206,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585672</v>
+        <v>585673</v>
       </c>
       <c r="R54" t="n">
-        <v>7059874</v>
+        <v>7059863</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6303,50 +6268,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265542</v>
+        <v>125265762</v>
       </c>
       <c r="B55" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585673</v>
+        <v>585766</v>
       </c>
       <c r="R55" t="n">
-        <v>7059863</v>
+        <v>7059797</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6405,15 +6370,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265649</v>
+        <v>125265916</v>
       </c>
       <c r="B56" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56227</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6421,34 +6381,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585700</v>
+        <v>585837</v>
       </c>
       <c r="R56" t="n">
-        <v>7059842</v>
+        <v>7059893</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6507,15 +6472,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125265038</v>
+        <v>125265666</v>
       </c>
       <c r="B57" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,21 +6483,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6507,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>585638</v>
+        <v>585701</v>
       </c>
       <c r="R57" t="n">
-        <v>7059956</v>
+        <v>7059838</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5776,7 +5776,7 @@
         <v>125265495</v>
       </c>
       <c r="B50" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>125265649</v>
       </c>
       <c r="B51" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>125265038</v>
       </c>
       <c r="B52" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>125265542</v>
       </c>
       <c r="B54" t="n">
-        <v>91575</v>
+        <v>91582</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>125265666</v>
       </c>
       <c r="B57" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -5776,7 +5776,7 @@
         <v>125265495</v>
       </c>
       <c r="B50" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>125265649</v>
       </c>
       <c r="B51" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>125265038</v>
       </c>
       <c r="B52" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>125265542</v>
       </c>
       <c r="B54" t="n">
-        <v>91582</v>
+        <v>91586</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6268,10 +6268,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265762</v>
+        <v>125265916</v>
       </c>
       <c r="B55" t="n">
-        <v>57648</v>
+        <v>56227</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6279,27 +6279,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6308,10 +6308,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585766</v>
+        <v>585837</v>
       </c>
       <c r="R55" t="n">
-        <v>7059797</v>
+        <v>7059893</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6370,10 +6370,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125265916</v>
+        <v>125265762</v>
       </c>
       <c r="B56" t="n">
-        <v>56227</v>
+        <v>57648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6381,27 +6381,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>585837</v>
+        <v>585766</v>
       </c>
       <c r="R56" t="n">
-        <v>7059893</v>
+        <v>7059797</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6475,7 +6475,7 @@
         <v>125265666</v>
       </c>
       <c r="B57" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6567,6 +6567,107 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126074348</v>
+      </c>
+      <c r="B58" t="n">
+        <v>88641</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>510</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tågsjöberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>585779</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7059930</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6572,7 +6572,7 @@
         <v>126074348</v>
       </c>
       <c r="B58" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6572,7 +6572,7 @@
         <v>126074348</v>
       </c>
       <c r="B58" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6572,7 +6572,7 @@
         <v>126074348</v>
       </c>
       <c r="B58" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6572,7 +6572,7 @@
         <v>126074348</v>
       </c>
       <c r="B58" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 40277-2024 artfynd.xlsx
+++ b/artfynd/A 40277-2024 artfynd.xlsx
@@ -6572,7 +6572,7 @@
         <v>126074348</v>
       </c>
       <c r="B58" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
